--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5950,6 +5950,33 @@
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Plan surface — architecture settled; brief v2 written</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>FOUNDER SETTLED THE PLAN ARCHITECTURE; brief bumped to mockups/Plan-redesign-Aug-12/PLAN-REDESIGN-BRIEF-v2-2026-08-12.md (v1 kept, superseded). DECIDED: (1) the Plan tab is TWO sections — "Your retirement plan" and "Decisions you can make today" — with "When can I retire?" in section 1, because it is the retire-at input wearing a question mark. (2) Section 1 is ONE MERGED SCREEN: the three answer questions + the What-if sandbox + the read-only drivers + the big-one-time-costs list, every field prefilled from a default or a calculation, anything genuinely unknown LABELLED as missing with a way to add it. Retire-at default 65 and plan-to default 90 become VISIBLE and changeable (they are already the code defaults but were applied silently). Retirement spending gets ASKED plainly, prefilled from today's spending — the app currently derives it and then tells the person "you set it", which is not true. (3) NEW RULE — facts save, choices commit: age/spending/what-counts/big-costs save on the spot; retire-at, claim age and extra saving stay drafts until "Use as my plan". (4) The outcome is two figures plus a line: the odds sentence, a goal tracker against a TARGET NEST EGG, and the yearly saving needed. The target is COMPUTED (the pile that puts the odds at 80%, the Likely boundary), not typed — a typed number stays as an optional marked override — so the tracker and the gauge are one fact drawn twice and can never contradict each other. The required saving is shown against the tax-advantaged room the app already knows. (5) The IMPOSSIBLE-REQUIRED-SAVING state is a required design: when the honest number exceeds what the person earns, say it plainly then pivot to the three levers that move (retire later, spend less, claim later) — never "you have failed". (6) The outcome must stay visible on a long screen. (7) What-if is absorbed and deleted; Multi-goal, Roth, Social Security timing, required withdrawals and the stress test survive in section 2, each row earning its place by saying what it is worth in dollars or points.</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12, across three exchanges: the six retirement inputs + defaults 65/90; the two-section layout; then "combine plan answers and Try what-ifs into one screen… add a big one-time cost… reverse calculate the monthly/annual savings goal based on targeted retirement nest egg" — with my recommendation to DERIVE the target from the odds rather than take a typed number, accepted.</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5977,6 +5977,33 @@
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>The odds — the verdict word is removed, app-wide</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>THE WORD IS GONE. The odds now read "60% odds of lasting to age 90" with nothing in front. Removed on all seven surfaces that showed it — Home, Net worth, Plan hub, Plan answers, Will it last, Cash flow, Multi-goal — plus the desktop sandbox and the spoken screen-reader labels. BOTH rival word-sets are deleted from the code (Likely/Uncertain/Unlikely and the retiree Holding/Watch closely/Running short), which also closes the inconsistency where one retiree at 100% read "Holding" on the Plan tab and "Likely" on Will-it-last. The Multi-goal row that read "Uncertain to Uncertain" is gone — the row above it already says 60% to 67%. The info dot no longer defines a word that does not exist: it now opens WHAT THE NUMBER MEANS and says plainly why no word sits beside the percentage. Tests rewritten to pin the ABSENCE of the words on every surface, and the cross-screen agreement pin now reads the accessibility labels (what a screen reader hears) instead of hunting for a word beside a number — a stronger pin, because it fails if a screen shows the number without saying what it is. Gates: 1565 tests green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12: "let's not say Uncertain — 60% odds of lasting to age 90. uncertain and giving it 60% probability does not make sense. it should be either or. Let's remove uncertain." Applied to all three bands and both voices, not just the middle word — the same objection holds for "Likely — 85%", and keeping one word while dropping another would have been worse than either.</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6006,6 +6006,33 @@
       <c r="E116" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Plan redesign — Claude Design handoff received and reviewed</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>HANDOFF IN (Plan-requirements.md + Plan.dc.html), reviewed against the code; review saved at mockups/Plan-redesign-Aug-12/HANDOFF-REVIEW-2026-08-12.md. ADOPTED as drawn: the two-gauge hero (odds left, assets-vs-target right, both dollar figures beneath, then the bridge sentence "add $38,000/yr for 7 years to reach your target and raise your odds to 80%"), FACT/DRAFT chips as the at-a-glance tell between a saved fact and a draft choice, all five states of the merged screen with a pinned outcome strip, the honest impossible-saving state with three levers, worth-labelled Section 2 rows, and the retiree paycheck variant in place of a target gauge. FIVE CORRECTIONS before code: (1) BLOCKING — the design puts the verdict word on every screen ("Uncertain — 60% odds…"); the founder deleted the word hours after the brief went out, so every such line loses its word and nothing else moves. Not the designer's error: brief v2 asked them to pick a word-set; the sequencing was mine. (2) The handoff calls the 31-87% range a confidence band on the estimate and forbids saying "your odds could be as low as 31%" — but our engine derives that band by re-running the whole simulation at 2 percentage points lower and higher assumed return, so it IS a market-outcome range; the shipped wording "across bad-to-good markets" is correct and theirs would be false. (3) It puts the home's 4.5% growth into the blended return of a portfolio that excludes the home. (4) June's "spend more" row says "+$1,600/mo room" where the handoff's own arithmetic gives $2,555 unused safe draw — $1,600 is what she IS using. (5) The empty-state sample shows 74%; the app's sample is 84%, used everywhere. NEW ENGINE WORK identified (does not exist today): the derived target solved backwards for 80% odds, the required annual saving, per-lever point deltas, goals/debt wired into the odds engine for Section 2 labels, and the draft-vs-committed state layer — with a performance risk when one stepper move triggers a target solve plus a saving solve plus three lever runs. OPEN QUESTION for the founder: the handoff puts the merged screen behind a link from the tab rather than inside it, so the tab is a summary and the inputs are one tap away — that decides whether a person can change their retire age without leaving the tab.</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12 handed over the Claude Design output for the Plan surface.</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12) · review by me</t>
         </is>
       </c>
     </row>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6033,6 +6033,33 @@
       <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12) · review by me</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Plan outcome — one score, then arithmetic (second gauge dropped)</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>BUILDING THE ENGINE KILLED THE SECOND GAUGE. src/domain/planning/target.ts solves the odds backwards: targetAtRetirement (the pot on day one of retirement that reaches 80% odds, by bisection on the same 400-path simulation), requiredAnnualSaving (a second solve on the real plan, returned as the EXTRA over what they already save), and leverDeltas (each lever a genuine re-run with one change; claiming later raises the CHECK by 8%/yr, and the lever is hidden entirely when there is no Social Security on file). 11 engine tests incl. a speed budget — the whole outcome block is 238ms. THE FINDING: run a struggling person through it and the design contradicts itself — 31% odds beside a target gauge reading 80% of the way. Deriving the target does NOT prevent this, because progress compares ONE future (the median) against a threshold while the odds count how many of 400 futures lasted; the spread is what separates them. Founder accepted the fix: the right-hand side stops being a rival percentage. Asked whether it should be a gauge, a bar or text, the answer is TEXT — any proportional shape IS a score, and the eye believes the shape even after the number is removed. So: ONE score (the odds gauge), then three money lines that subtract to each other — On track for / Target nest egg (founder's words, replacing "You'd need") / Short — with the shortfall bold, then the bridge sentence naming the yearly amount and how much fits in tax-advantaged room. Above 100% the third line flips to "More than you need", which a gauge could not have drawn. The impossible state says the honest number once and turns to the levers. Built as src/components/PlanOutcome.tsx with 7 tests (one-score pin, the arithmetic ties to the dollar, the ahead state, the bridge, the impossible state, hide-balances, and the nothing-computable state). Mock deviation logged: the handoff's illustrative 60% / $1.9M / $38,000 do not survive contact with the engine — Pat as specified is 81% with a $1.14M target.</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12: "I am on with $" (the dollar gap over a second percentage), then "from design perspective is it still gauge or bar or simple text?" → text, and "It should not be You'd need - it is the Target Nest Egg."</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
         </is>
       </c>
     </row>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6058,6 +6058,33 @@
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Plan tab rebuilt — two sections, inputs ON the tab</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>SECTION 1 IS THE TAB, not a link behind it (founder ruling: "inputs on the tab"). The Plan tab now reads: YOUR RETIREMENT PLAN band → the outcome (one score, then On track for / Target nest egg / Short, then the bridge sentence) → FACTS — SAVE AS YOU GO (age, monthly spending in retirement, what counts, big one-time costs) → CHOICES — TRY THEM, NOTHING CHANGES YET (retire at, plan to age, extra saving) → DECISIONS YOU CAN MAKE TODAY. The draft layer lives at the tab so a stepper moves the number above it live (walked: 55% → 62% on one press of Retire at, with the projection and target moving too); "Use as my plan" confirms and writes. FOUR DEFECTS FOUND BY WALKING THE BUILT SCREEN, all fixed before reporting: (1) the outcome printed "More than you need $74,845" beside "Adding $43,000 a year closes it" — the median can clear the target while the odds do not, so the gap line now stands down whenever its sign disagrees with the odds and the bridge speaks alone; (2) the old narrative pair ("You could retire at 65 with…" + "…if you retire at 65, and spend $5,200/mo — your planned spending, you set it") was deleted: it repeated what the block above now says, did not follow the draft, and claimed "you set it" of a figure the app had derived; (3) the "Try what-ifs — a sandbox" door removed — the steppers ARE the sandbox, sitting under the number they move, so four sandboxes became one; (4) "When can I retire?" and "What big costs are coming?" removed from the decision list — both now live in section 1, and three copies of one question is how it got confusing. Gates: 1593 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12: "inputs on the tab." then "continue".</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
         </is>

--- a/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
+++ b/docs/snapshots/FCC-core-detailed-design-v1.3-2026-08-12.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6085,6 +6085,33 @@
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>/plan-answers folded into the Plan tab — one component, two states</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>THE LAST DUPLICATE IS GONE. The separate /plan-answers screen and route are DELETED; the Plan tab now carries the two states the Claude Design handoff drew as "Section 1 — Missing Age" and "Section 1 — Empty Sample": the age/spending row wears an amber MISSING chip, the choice steppers stand down (nothing for a choice to change yet), and a dashed box replaces the odds — "Your odds — can't work them out yet. Add what you spend below." Home and Net worth now deep-link to /(tabs)/plan?focus=&lt;the missing answer&gt; instead of a second screen; the tab reads the focus param and marks that row. The three ways in (connect / import / by hand) came back from the shared DOORS list — the fold had dropped them, which would have left someone with no accounts no way to add one; a source-pin test caught it. The route guard entry was removed with the route, and every test that pinned the deleted screen was MOVED onto the tab rather than deleted, including the cross-surface sameness pin, which now reads the spoken labels so a screen that shows the number without saying what it is fails. Gates: 1592 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12, on my own flag that two components were doing one job: "which screen in this in the plan-dc-html?" then "yes" to folding it before the cut. The handoff already had it right — plan-answers was never a screen in the design, only two states of Section 1.</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
         </is>
